--- a/docs/第三次作业_关欣/404烦恼未找到_系统设计与数据库设计评审表.xlsx
+++ b/docs/第三次作业_关欣/404烦恼未找到_系统设计与数据库设计评审表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mayday\Desktop\学习工作相关\软件工程实践\第三次团队作业\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\大学\软件工程\共享\404NOTFOUND\docs\第三次作业_关欣\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4CF741-07AC-4850-85ED-C4EC86E701F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AA42FD-3C3F-4612-9BFC-8B3B08448856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="评审表_现场" sheetId="2" r:id="rId1"/>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -271,27 +269,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +596,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -635,10 +633,10 @@
       <c r="N1" s="9"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2">
         <v>10</v>
       </c>
@@ -664,10 +662,10 @@
         <f>ROUND(SUM(C2:I2),2)</f>
         <v>100</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -726,7 +724,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="5" t="str">
-        <f>IF(COUNT(C4:I4)=7,ROUND(SUMPRODUCT($C$2:$I$2,C4:I4)*20,1),"")</f>
+        <f t="shared" ref="J4:J13" si="0">IF(COUNT(C4:I4)=7,ROUND(SUMPRODUCT($C$2:$I$2,C4:I4)*20,1),"")</f>
         <v/>
       </c>
       <c r="K4" s="6"/>
@@ -747,7 +745,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="5" t="str">
-        <f>IF(COUNT(C5:I5)=7,ROUND(SUMPRODUCT($C$2:$I$2,C5:I5)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K5" s="6"/>
@@ -768,7 +766,7 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="5" t="str">
-        <f>IF(COUNT(C6:I6)=7,ROUND(SUMPRODUCT($C$2:$I$2,C6:I6)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K6" s="6"/>
@@ -789,7 +787,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="5" t="str">
-        <f>IF(COUNT(C7:I7)=7,ROUND(SUMPRODUCT($C$2:$I$2,C7:I7)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K7" s="6"/>
@@ -810,7 +808,7 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="5" t="str">
-        <f>IF(COUNT(C8:I8)=7,ROUND(SUMPRODUCT($C$2:$I$2,C8:I8)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K8" s="6"/>
@@ -831,7 +829,7 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="5" t="str">
-        <f>IF(COUNT(C9:I9)=7,ROUND(SUMPRODUCT($C$2:$I$2,C9:I9)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K9" s="6"/>
@@ -852,7 +850,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="5" t="str">
-        <f>IF(COUNT(C10:I10)=7,ROUND(SUMPRODUCT($C$2:$I$2,C10:I10)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K10" s="6"/>
@@ -873,7 +871,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="5" t="str">
-        <f>IF(COUNT(C11:I11)=7,ROUND(SUMPRODUCT($C$2:$I$2,C11:I11)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K11" s="6"/>
@@ -894,7 +892,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="5" t="str">
-        <f>IF(COUNT(C12:I12)=7,ROUND(SUMPRODUCT($C$2:$I$2,C12:I12)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K12" s="6"/>
@@ -915,7 +913,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="5" t="str">
-        <f>IF(COUNT(C13:I13)=7,ROUND(SUMPRODUCT($C$2:$I$2,C13:I13)*20,1),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K13" s="6"/>
@@ -923,104 +921,62 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5" t="str">
-        <f>IF(COUNT(C14:I14)=7,ROUND(SUMPRODUCT($C$2:$I$2,C14:I14)*20,1),"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-    </row>
-    <row r="15" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5" t="str">
-        <f>IF(COUNT(C15:I15)=7,ROUND(SUMPRODUCT($C$2:$I$2,C15:I15)*20,1),"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-    </row>
-    <row r="16" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="14" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="7">
-        <f t="shared" ref="C16:I16" si="0">COUNT(C$4:C$15)</f>
+      <c r="B14" s="16"/>
+      <c r="C14" s="7">
+        <f>COUNT(C$4:C$13)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="7">
-        <f t="shared" si="0"/>
+      <c r="D14" s="7">
+        <f>COUNT(D$4:D$13)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="7">
-        <f t="shared" si="0"/>
+      <c r="E14" s="7">
+        <f>COUNT(E$4:E$13)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="7">
-        <f t="shared" si="0"/>
+      <c r="F14" s="7">
+        <f>COUNT(F$4:F$13)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="7">
-        <f t="shared" si="0"/>
+      <c r="G14" s="7">
+        <f>COUNT(G$4:G$13)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="7">
-        <f t="shared" si="0"/>
+      <c r="H14" s="7">
+        <f>COUNT(H$4:H$13)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="7">
-        <f t="shared" si="0"/>
+      <c r="I14" s="7">
+        <f>COUNT(I$4:I$13)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="1" t="str">
-        <f>IF(COUNT(J4:J15)=0,"",ROUND(AVERAGE(J4:J15),1))</f>
-        <v/>
-      </c>
-      <c r="K16" s="12" t="str">
-        <f>"已填分数 "&amp;COUNT(C4:I15)&amp;" 个 / 已评组数 "&amp;COUNT(J4:J15)&amp;" 组 / 总分平均 "&amp;IF(COUNT(J4:J15)=0,"未评",TEXT(AVERAGE(J4:J15),"0.0")&amp;" 分")</f>
+      <c r="J14" s="1" t="str">
+        <f>IF(COUNT(J4:J13)=0,"",ROUND(AVERAGE(J4:J13),1))</f>
+        <v/>
+      </c>
+      <c r="K14" s="17" t="str">
+        <f>"已填分数 "&amp;COUNT(C4:I13)&amp;" 个 / 已评组数 "&amp;COUNT(J4:J13)&amp;" 组 / 总分平均 "&amp;IF(COUNT(J4:J13)=0,"未评",TEXT(AVERAGE(J4:J13),"0.0")&amp;" 分")</f>
         <v>已填分数 0 个 / 已评组数 0 组 / 总分平均 未评</v>
       </c>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="K14:N14"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="分数超出范围" error="只能输入 1～5 的整数，不能输入小数、0、负数或其他字符。" promptTitle="评分 1～5 分（5 最好）" prompt="请输入 1～5 的整数：5 最好、1 最差。同一项对全部小组用同一锚点；无把握可留空，留空不参与总分。" sqref="C4:I15" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="分数超出范围" error="只能输入 1～5 的整数，不能输入小数、0、负数或其他字符。" promptTitle="评分 1～5 分（5 最好）" prompt="请输入 1～5 的整数：5 最好、1 最差。同一项对全部小组用同一锚点；无把握可留空，留空不参与总分。" sqref="C4:I13" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -1038,7 +994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1082,7 +1038,7 @@
         <v/>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D14" si="0">IF(N(C3)=0,"",_xlfn.RANK.EQ(C3,$C$3:$C$14,0))</f>
+        <f>IF(N(C3)=0,"",_xlfn.RANK.EQ(C3,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1055,7 @@
         <v/>
       </c>
       <c r="D4" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C4)=0,"",_xlfn.RANK.EQ(C4,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1072,7 @@
         <v/>
       </c>
       <c r="D5" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C5)=0,"",_xlfn.RANK.EQ(C5,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1089,7 @@
         <v/>
       </c>
       <c r="D6" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C6)=0,"",_xlfn.RANK.EQ(C6,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1106,7 @@
         <v/>
       </c>
       <c r="D7" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C7)=0,"",_xlfn.RANK.EQ(C7,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1123,7 @@
         <v/>
       </c>
       <c r="D8" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C8)=0,"",_xlfn.RANK.EQ(C8,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1184,7 +1140,7 @@
         <v/>
       </c>
       <c r="D9" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C9)=0,"",_xlfn.RANK.EQ(C9,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1201,7 +1157,7 @@
         <v/>
       </c>
       <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C10)=0,"",_xlfn.RANK.EQ(C10,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1218,7 +1174,7 @@
         <v/>
       </c>
       <c r="D11" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C11)=0,"",_xlfn.RANK.EQ(C11,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
@@ -1235,41 +1191,7 @@
         <v/>
       </c>
       <c r="D12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="str">
-        <f>IF(评审表_现场!B14="","",评审表_现场!B14)</f>
-        <v/>
-      </c>
-      <c r="C13" s="5" t="str">
-        <f>评审表_现场!J14</f>
-        <v/>
-      </c>
-      <c r="D13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="str">
-        <f>IF(评审表_现场!B15="","",评审表_现场!B15)</f>
-        <v/>
-      </c>
-      <c r="C14" s="5" t="str">
-        <f>评审表_现场!J15</f>
-        <v/>
-      </c>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(N(C12)=0,"",_xlfn.RANK.EQ(C12,$C$3:$C$12,0))</f>
         <v/>
       </c>
     </row>
